--- a/stories/arbres/TREE-DIF-031.xlsx
+++ b/stories/arbres/TREE-DIF-031.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Hugo est avec papa, dans la chambre. Hugo a envie de jouer. papa est là, tout près. On va apprendre : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo écoute papa. Hugo entend les mots : proposer, accepter plusieurs réponses.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Hugo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On montre du doigt, sans courir. papa dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Hugo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Hugo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On montre du doigt, sans courir.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; accepter. Hugo respire. Hugo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3944,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4111,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4278,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4445,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de la cuisine, le livre et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4612,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4779,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4946,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5113,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5304,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5471,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5638,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5805,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5972,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6139,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6306,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6335,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Hugo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On rit un peu. papa dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Hugo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6473,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Hugo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On rit un peu.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6659,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6832,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; accepter. Hugo respire. Hugo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7023,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7190,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le jardin, les cubes et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le jardin, les cubes et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le jardin, le livre et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. La couverture est douce. On se tient la main. Cette fin-là est celle de le jardin, le livre et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10268,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le jardin, la dînette et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10435,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10602,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10769,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10936,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. On entend un oiseau. On se tient la main. Cette fin-là est celle de le jardin, la dînette et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11103,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11132,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Hugo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On se tait une seconde. papa dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Hugo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11270,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Hugo se souvient : proposer, accepter plusieurs réponses. Voici le geste : inviter ; accepter. On se tait une seconde.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11456,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11629,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; accepter. Hugo respire. Hugo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11820,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11987,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12178,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12345,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12512,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12679,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de la chambre, les cubes et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12846,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13013,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. La couverture est douce. On range un objet. Cette fin-là est celle de la chambre, les cubes et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13180,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13347,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13538,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13705,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13872,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14039,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. La couverture est douce. On se tient la main. Cette fin-là est celle de la chambre, le livre et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14206,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14373,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. On entend un oiseau. On range un objet. Cette fin-là est celle de la chambre, le livre et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14540,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14707,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14898,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15065,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15232,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15399,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. On entend un oiseau. On se tient la main. Cette fin-là est celle de la chambre, la dînette et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15566,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15733,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la chambre, la dînette et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15900,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-031.xlsx
+++ b/stories/arbres/TREE-DIF-031.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Hugo est avec papa, dans la chambre. Hugo a envie de jouer. papa est là, tout près. On va apprendre : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo écoute papa. Hugo entend les mots : proposer, accepter plusieurs réponses.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; accepter. Hugo respire. Hugo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Hugo a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Hugo rejoint le matin. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Hugo rejoint le soir. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Hugo a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3949,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4116,6 +4137,7 @@
           <t>narrateur|Hugo rejoint le matin. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4283,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4450,6 +4473,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de la cuisine, le livre et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4617,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4809,7 @@
           <t>narrateur|Hugo rejoint le soir. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5145,7 @@
           <t>narrateur|Hugo a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5476,6 +5505,7 @@
           <t>narrateur|Hugo rejoint le matin. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5841,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6177,7 @@
           <t>narrateur|Hugo rejoint le soir. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6666,6 +6702,7 @@
           <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6874,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; accepter. Hugo respire. Hugo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Hugo a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|Hugo rejoint le matin. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le jardin, les cubes et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Hugo rejoint le soir. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le jardin, les cubes et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Hugo a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Hugo rejoint le matin. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le jardin, le livre et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Hugo rejoint le soir. La couverture est douce. On se tient la main. Cette fin-là est celle de le jardin, le livre et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Hugo a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10273,6 +10330,7 @@
           <t>narrateur|Hugo rejoint le matin. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le jardin, la dînette et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10666,7 @@
           <t>narrateur|Hugo rejoint après la sieste. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11002,7 @@
           <t>narrateur|Hugo rejoint le soir. On entend un oiseau. On se tient la main. Cette fin-là est celle de le jardin, la dînette et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11463,6 +11527,7 @@
           <t>narrateur|Que fait-on ? Inviter sans forcer.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11634,6 +11699,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; accepter. Hugo respire. Hugo retient : proposer, accepter plusieurs réponses. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11891,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12059,7 @@
           <t>narrateur|Hugo a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12251,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12350,6 +12419,7 @@
           <t>narrateur|Hugo rejoint le matin. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12587,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12755,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de la chambre, les cubes et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12923,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13091,7 @@
           <t>narrateur|Hugo rejoint le soir. La couverture est douce. On range un objet. Cette fin-là est celle de la chambre, les cubes et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13259,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13427,7 @@
           <t>narrateur|Hugo a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13543,6 +13619,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13710,6 +13787,7 @@
           <t>narrateur|Hugo rejoint le matin. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13877,6 +13955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14044,6 +14123,7 @@
           <t>narrateur|Hugo rejoint après la sieste. La couverture est douce. On se tient la main. Cette fin-là est celle de la chambre, le livre et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14211,6 +14291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14378,6 +14459,7 @@
           <t>narrateur|Hugo rejoint le soir. On entend un oiseau. On range un objet. Cette fin-là est celle de la chambre, le livre et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14545,6 +14627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14795,7 @@
           <t>narrateur|Hugo a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : inviter ; accepter. Hugo répète tout bas : proposer, accepter plusieurs réponses. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14903,6 +14987,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15070,6 +15155,7 @@
           <t>narrateur|Hugo rejoint le matin. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et le matin. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15491,7 @@
           <t>narrateur|Hugo rejoint après la sieste. On entend un oiseau. On se tient la main. Cette fin-là est celle de la chambre, la dînette et après la sieste. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15827,7 @@
           <t>narrateur|Hugo rejoint le soir. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la chambre, la dînette et le soir. Hugo a appris : Inviter sans forcer. Voici le geste : inviter ; accepter. Hugo a entendu : proposer, accepter plusieurs réponses. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +15995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16038,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16253,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-031.xlsx
+++ b/stories/arbres/TREE-DIF-031.xlsx
@@ -3897,12 +3897,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou plus tard ?</t>
+          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou garder une tomate ?</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou plus tard ?</t>
+          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou garder une tomate ?</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|Nina reste collée à l'ombre du figuier.
-maman|L'eau, l'ombre des plants, ou plus tard ?</t>
+maman|L'eau, l'ombre des plants, ou garder une tomate ?</t>
         </is>
       </c>
     </row>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Le caillou blanc veille entre les tomates. Tu as dit oui, avec lui. Il a tout vu, du panier. Vous avez cueilli sans tirer. Goûtez un peu, tout doux. Le chapeau de paille sèche sur la marche. Nina croque, le jus lui tache le menton. Reste autant que tu veux. Le sel brille déjà sur la marche.</t>
+          <t>Le caillou blanc veille entre les tomates. Tu as dit oui, avec lui. Il a tout vu, du chapeau. Vous avez cueilli sans tirer. Goûtez un peu, tout doux. Le chapeau de paille sèche sur la marche. Nina croque, le jus lui tache le menton. Reste autant que tu veux. Le sel brille déjà sur la marche.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Le caillou blanc veille entre les tomates. Tu as dit oui, avec lui. Il a tout vu, du panier. Vous avez cueilli sans tirer. Goûtez un peu, tout doux. Le chapeau de paille sèche sur la marche. Nina croque, le jus lui tache le menton. Reste autant que tu veux. Le sel brille déjà sur la marche.</t>
+          <t>Le caillou blanc veille entre les tomates. Tu as dit oui, avec lui. Il a tout vu, du chapeau. Vous avez cueilli sans tirer. Goûtez un peu, tout doux. Le chapeau de paille sèche sur la marche. Nina croque, le jus lui tache le menton. Reste autant que tu veux. Le sel brille déjà sur la marche.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -8327,7 +8327,7 @@
         <is>
           <t>narrateur|Le caillou blanc veille entre les tomates.
 enfant-m|Tu as dit oui, avec lui.
-copine|Il a tout vu, du panier.
+copine|Il a tout vu, du chapeau.
 papa|Vous avez cueilli sans tirer.
 maman|Goûtez un peu, tout doux.
 narrateur|Le chapeau de paille sèche sur la marche.
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou plus tard ?</t>
+          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou garder une tomate ?</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou plus tard ?</t>
+          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou garder une tomate ?</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -9050,7 +9050,7 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|Nina reste collée à l'ombre du figuier.
-maman|L'eau, l'ombre des plants, ou plus tard ?</t>
+maman|L'eau, l'ombre des plants, ou garder une tomate ?</t>
         </is>
       </c>
     </row>
@@ -10127,12 +10127,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Le chapeau de paille pose une paille d'ombre sur le bac. Nina patouille un gâteau de sable. Il n'est pas cuit, encore. Les tomates m'attendent. Le gâteau penche, tout mouillé. Tu viens cueillir ? Après, peut-être. Son gâteau n'est pas fini. Tu proposes quoi, Raphaël ?</t>
+          <t>Le chapeau de paille fait un rond sur le bac. Nina patouille un gâteau de sable. Il n'est pas cuit, encore. Les tomates m'attendent. Le gâteau penche, tout mouillé. Tu viens cueillir ? Après, peut-être. Son gâteau n'est pas fini. Tu proposes quoi, Raphaël ?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Le chapeau de paille pose une paille d'ombre sur le bac. Nina patouille un gâteau de sable. Il n'est pas cuit, encore. Les tomates m'attendent. Le gâteau penche, tout mouillé. Tu viens cueillir ? Après, peut-être. Son gâteau n'est pas fini. Tu proposes quoi, Raphaël ?</t>
+          <t>Le chapeau de paille fait un rond sur le bac. Nina patouille un gâteau de sable. Il n'est pas cuit, encore. Les tomates m'attendent. Le gâteau penche, tout mouillé. Tu viens cueillir ? Après, peut-être. Son gâteau n'est pas fini. Tu proposes quoi, Raphaël ?</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -10267,7 +10267,7 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Le chapeau de paille pose une paille d'ombre sur le bac.
+          <t>narrateur|Le chapeau de paille fait un rond sur le bac.
 narrateur|Nina patouille un gâteau de sable.
 copine|Il n'est pas cuit, encore.
 enfant-m|Les tomates m'attendent.
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Le caillou blanc veille entre les tomates. Tu as dit oui, avec lui. Il a tout vu, du panier. Vous avez cueilli sans tirer. Goûtez un peu, tout doux. Le petit tabouret reste près du pain. Nina croque, le jus lui tache le menton. Reste autant que tu veux. Le sel brille déjà sur la marche.</t>
+          <t>Le caillou blanc veille entre les tomates. Tu as dit oui, avec lui. Il a tout vu, du tabouret. Vous avez cueilli sans tirer. Goûtez un peu, tout doux. Le petit tabouret reste près du pain. Nina croque, le jus lui tache le menton. Reste autant que tu veux. Le sel brille déjà sur la marche.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Le caillou blanc veille entre les tomates. Tu as dit oui, avec lui. Il a tout vu, du panier. Vous avez cueilli sans tirer. Goûtez un peu, tout doux. Le petit tabouret reste près du pain. Nina croque, le jus lui tache le menton. Reste autant que tu veux. Le sel brille déjà sur la marche.</t>
+          <t>Le caillou blanc veille entre les tomates. Tu as dit oui, avec lui. Il a tout vu, du tabouret. Vous avez cueilli sans tirer. Goûtez un peu, tout doux. Le petit tabouret reste près du pain. Nina croque, le jus lui tache le menton. Reste autant que tu veux. Le sel brille déjà sur la marche.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13315,7 +13315,7 @@
         <is>
           <t>narrateur|Le caillou blanc veille entre les tomates.
 enfant-m|Tu as dit oui, avec lui.
-copine|Il a tout vu, du panier.
+copine|Il a tout vu, du tabouret.
 papa|Vous avez cueilli sans tirer.
 maman|Goûtez un peu, tout doux.
 narrateur|Le petit tabouret reste près du pain.
@@ -13873,12 +13873,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou plus tard ?</t>
+          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou garder une tomate ?</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou plus tard ?</t>
+          <t>Nina reste collée à l'ombre du figuier. L'eau, l'ombre des plants, ou garder une tomate ?</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -14038,7 +14038,7 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|Nina reste collée à l'ombre du figuier.
-maman|L'eau, l'ombre des plants, ou plus tard ?</t>
+maman|L'eau, l'ombre des plants, ou garder une tomate ?</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16576,6 +16576,20 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
